--- a/public/downloads/TangFrom2020.xlsx
+++ b/public/downloads/TangFrom2020.xlsx
@@ -8,19 +8,21 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="MATLANTISv8" sheetId="7" r:id="rId7"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="MATLANTISv8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="58">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -52,10 +54,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -127,6 +129,27 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>CO</t>
   </si>
   <si>
@@ -145,34 +168,34 @@
     <t>C</t>
   </si>
   <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>CH2</t>
+  </si>
+  <si>
+    <t>CH3</t>
+  </si>
+  <si>
     <t>CHOH</t>
+  </si>
+  <si>
+    <t>COOH</t>
   </si>
   <si>
     <t>HCOO</t>
   </si>
   <si>
-    <t>CH3</t>
-  </si>
-  <si>
-    <t>CH2</t>
-  </si>
-  <si>
-    <t>CH</t>
-  </si>
-  <si>
-    <t>COOH</t>
-  </si>
-  <si>
-    <t>H2COO</t>
+    <t>CH2O</t>
   </si>
   <si>
     <t>CH2OH</t>
   </si>
   <si>
-    <t>CH2O</t>
+    <t>CH3O</t>
   </si>
   <si>
-    <t>CH3O</t>
+    <t>H2COO</t>
   </si>
 </sst>
 </file>
@@ -658,10 +681,10 @@
         <v>170</v>
       </c>
       <c r="N3" s="5">
-        <v>1606.552889585495</v>
+        <v>1606552.889585495</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03241959216195127</v>
+        <v>32.41959216195127</v>
       </c>
       <c r="P3" s="5">
         <v>49555</v>
@@ -708,10 +731,10 @@
         <v>170</v>
       </c>
       <c r="N4" s="5">
-        <v>1197.881508827209</v>
+        <v>1197881.508827209</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04246451518406216</v>
+        <v>42.46451518406217</v>
       </c>
       <c r="P4" s="5">
         <v>28209</v>
@@ -758,10 +781,10 @@
         <v>170</v>
       </c>
       <c r="N5" s="5">
-        <v>2177.729719161987</v>
+        <v>2177729.719161987</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1323767381412672</v>
+        <v>132.3767381412673</v>
       </c>
       <c r="P5" s="5">
         <v>16451</v>
@@ -808,10 +831,10 @@
         <v>100</v>
       </c>
       <c r="N6" s="5">
-        <v>871.2131252288818</v>
+        <v>871213.1252288818</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08149795371645294</v>
+        <v>81.49795371645294</v>
       </c>
       <c r="P6" s="5">
         <v>10690</v>
@@ -858,10 +881,10 @@
         <v>170</v>
       </c>
       <c r="N7" s="5">
-        <v>1420.484217166901</v>
+        <v>1420484.217166901</v>
       </c>
       <c r="O7" s="4">
-        <v>0.08700748604476911</v>
+        <v>87.00748604476911</v>
       </c>
       <c r="P7" s="5">
         <v>16326</v>
@@ -889,6 +912,363 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>84.11764705882354</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.352941176470588</v>
+      </c>
+      <c r="D3" s="3">
+        <v>13.52941176470588</v>
+      </c>
+      <c r="E3" s="3">
+        <v>7.647058823529412</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.9013150146781537</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2054240254561325</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.920345950633251</v>
+      </c>
+      <c r="K3" s="4">
+        <v>78.26390556222488</v>
+      </c>
+      <c r="L3" s="4">
+        <v>83.02710883010873</v>
+      </c>
+      <c r="M3" s="5">
+        <v>170</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1606552.889585495</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.41959216195127</v>
+      </c>
+      <c r="P3" s="5">
+        <v>49555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>89.41176470588236</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.705882352941177</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.117647058823529</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2831289685130179</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2628259692953012</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3056527187606733</v>
+      </c>
+      <c r="K4" s="4">
+        <v>73.72488995598252</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.34491380444844</v>
+      </c>
+      <c r="M4" s="5">
+        <v>170</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1197881.508827209</v>
+      </c>
+      <c r="O4" s="4">
+        <v>42.46451518406217</v>
+      </c>
+      <c r="P4" s="5">
+        <v>28209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>91.76470588235294</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6.470588235294119</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2883404043000056</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2373130158865073</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3823950343759309</v>
+      </c>
+      <c r="K5" s="4">
+        <v>80.71488595438174</v>
+      </c>
+      <c r="L5" s="4">
+        <v>86.30313199105184</v>
+      </c>
+      <c r="M5" s="5">
+        <v>170</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2177729.719161987</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.3767381412673</v>
+      </c>
+      <c r="P5" s="5">
+        <v>16451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>89</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4464386417153018</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3800512299980651</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.5075730250506801</v>
+      </c>
+      <c r="K6" s="4">
+        <v>80.25408163265305</v>
+      </c>
+      <c r="L6" s="4">
+        <v>84.45447427293064</v>
+      </c>
+      <c r="M6" s="5">
+        <v>100</v>
+      </c>
+      <c r="N6" s="5">
+        <v>871213.1252288818</v>
+      </c>
+      <c r="O6" s="4">
+        <v>81.49795371645294</v>
+      </c>
+      <c r="P6" s="5">
+        <v>10690</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>93.52941176470588</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.294117647058823</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.294117647058823</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2044034332036722</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1989532938793529</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1882047353312603</v>
+      </c>
+      <c r="K7" s="4">
+        <v>79.49319727891152</v>
+      </c>
+      <c r="L7" s="4">
+        <v>85.59369653901783</v>
+      </c>
+      <c r="M7" s="5">
+        <v>170</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1420484.217166901</v>
+      </c>
+      <c r="O7" s="4">
+        <v>87.00748604476911</v>
+      </c>
+      <c r="P7" s="5">
+        <v>16326</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1001,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -1045,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -1202,9 +1582,324 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>143</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>23</v>
+      </c>
+      <c r="E3" s="5">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>152</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>156</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>8</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>89</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>159</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>9</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1215,9 +1910,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1251,8 +1952,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1274,10 +1983,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>0.79025702697876</v>
@@ -1315,10 +2042,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7201155342922902</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3709392188317555</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1122325583578079</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4">
         <v>2.350509477059339</v>
@@ -1356,10 +2101,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1093223060000706</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.295690978990532</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1647882791108143</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
         <v>0.3646150871771335</v>
@@ -1397,10 +2160,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3973663742923664</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1587239331253748</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1048738675060679</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
         <v>2.306256395684128</v>
@@ -1438,10 +2219,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-1.464221280582933</v>
+      </c>
+      <c r="O6" s="5">
+        <v>12</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.350143300163836</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1350254528315418</v>
+      </c>
+      <c r="R6" s="5">
+        <v>12</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4">
         <v>2.372434012604208</v>
@@ -1479,10 +2278,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.437545283056352</v>
+      </c>
+      <c r="O7" s="5">
+        <v>8</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.302248032531133</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.09981280796500869</v>
+      </c>
+      <c r="R7" s="5">
+        <v>8</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
         <v>1.539798711778531</v>
@@ -1520,92 +2337,146 @@
       <c r="M8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-1.539798711778531</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1693051140152875</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1693051140152875</v>
+      </c>
+      <c r="R8" s="5">
+        <v>8</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4">
-        <v>2.031844300240664</v>
+        <v>1.773777894377417</v>
       </c>
       <c r="C9" s="4">
-        <v>1.498088846462148</v>
+        <v>1.716175329592911</v>
       </c>
       <c r="D9" s="4">
-        <v>3.915710729569582</v>
+        <v>1.805118731856055</v>
       </c>
       <c r="E9" s="4">
-        <v>73.5204081632653</v>
+        <v>86.91751700680273</v>
       </c>
       <c r="F9" s="4">
-        <v>76.31991051454139</v>
+        <v>92.43288590604027</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
       </c>
       <c r="H9" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
         <v>1</v>
       </c>
       <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
         <v>1</v>
       </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-1.773777894377417</v>
+      </c>
+      <c r="O9" s="5">
+        <v>8</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.149077562000457</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.149077562000457</v>
+      </c>
+      <c r="R9" s="5">
+        <v>8</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" s="4">
-        <v>1.478408845395279</v>
+        <v>2.071528701252646</v>
       </c>
       <c r="C10" s="4">
-        <v>0.6855933308501595</v>
+        <v>1.856728901973838</v>
       </c>
       <c r="D10" s="4">
-        <v>6.032047840089035</v>
+        <v>2.043252257771201</v>
       </c>
       <c r="E10" s="4">
-        <v>78.1079931972789</v>
+        <v>84.48979591836735</v>
       </c>
       <c r="F10" s="4">
-        <v>83.53187919463087</v>
+        <v>89.29250559284115</v>
       </c>
       <c r="G10" s="5">
         <v>8</v>
       </c>
       <c r="H10" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
       </c>
       <c r="M10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-2.071528701252646</v>
+      </c>
+      <c r="O10" s="5">
+        <v>8</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1073998996394039</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1073998996394039</v>
+      </c>
+      <c r="R10" s="5">
+        <v>8</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4">
         <v>1.934663052587894</v>
@@ -1643,66 +2514,102 @@
       <c r="M11" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-1.934663052587894</v>
+      </c>
+      <c r="O11" s="5">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.06748076675444281</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.06748076675444281</v>
+      </c>
+      <c r="R11" s="5">
+        <v>8</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4">
-        <v>2.071528701252646</v>
+        <v>2.031844300240664</v>
       </c>
       <c r="C12" s="4">
-        <v>1.856728901973838</v>
+        <v>1.498088846462148</v>
       </c>
       <c r="D12" s="4">
-        <v>2.043252257771201</v>
+        <v>3.915710729569582</v>
       </c>
       <c r="E12" s="4">
-        <v>84.48979591836735</v>
+        <v>73.5204081632653</v>
       </c>
       <c r="F12" s="4">
-        <v>89.29250559284115</v>
+        <v>76.31991051454139</v>
       </c>
       <c r="G12" s="5">
         <v>8</v>
       </c>
       <c r="H12" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>-1.498088846462148</v>
+      </c>
+      <c r="O12" s="5">
         <v>6</v>
       </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
+      <c r="P12" s="4">
+        <v>0.9814868634648519</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.0976122640943989</v>
+      </c>
+      <c r="R12" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4">
-        <v>1.773777894377417</v>
+        <v>1.4541852397615</v>
       </c>
       <c r="C13" s="4">
-        <v>1.716175329592911</v>
+        <v>0.7983215883276509</v>
       </c>
       <c r="D13" s="4">
-        <v>1.805118731856055</v>
+        <v>5.138255648105769</v>
       </c>
       <c r="E13" s="4">
-        <v>86.91751700680273</v>
+        <v>76.84948979591837</v>
       </c>
       <c r="F13" s="4">
-        <v>92.43288590604027</v>
+        <v>81.7994966442953</v>
       </c>
       <c r="G13" s="5">
         <v>8</v>
@@ -1717,33 +2624,51 @@
         <v>1</v>
       </c>
       <c r="K13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
         <v>0</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>-0.7983215883276509</v>
+      </c>
+      <c r="O13" s="5">
+        <v>7</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.9556303868503164</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1144986723823478</v>
+      </c>
+      <c r="R13" s="5">
+        <v>7</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4">
-        <v>1.4541852397615</v>
+        <v>1.478408845395279</v>
       </c>
       <c r="C14" s="4">
-        <v>0.7983215883276509</v>
+        <v>0.6855933308501595</v>
       </c>
       <c r="D14" s="4">
-        <v>5.138255648105769</v>
+        <v>6.032047840089035</v>
       </c>
       <c r="E14" s="4">
-        <v>76.84948979591837</v>
+        <v>78.1079931972789</v>
       </c>
       <c r="F14" s="4">
-        <v>81.7994966442953</v>
+        <v>83.53187919463087</v>
       </c>
       <c r="G14" s="5">
         <v>8</v>
@@ -1766,25 +2691,43 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>-0.6855933308501595</v>
+      </c>
+      <c r="O14" s="5">
+        <v>7</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1.066424014914576</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.1168116201793333</v>
+      </c>
+      <c r="R14" s="5">
+        <v>7</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4">
-        <v>1.600154345833289</v>
+        <v>1.679205609867495</v>
       </c>
       <c r="C15" s="4">
-        <v>1.600154345833289</v>
+        <v>1.679205609867495</v>
       </c>
       <c r="D15" s="4">
-        <v>1.588674491249549</v>
+        <v>1.696029855320376</v>
       </c>
       <c r="E15" s="4">
-        <v>82.80612244897959</v>
+        <v>84.18367346938776</v>
       </c>
       <c r="F15" s="4">
-        <v>89.16107382550335</v>
+        <v>89.81543624161074</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1807,10 +2750,26 @@
       <c r="M15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4"/>
+      <c r="O15" s="5">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1.679205609867495</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>1.679205609867495</v>
+      </c>
+      <c r="R15" s="5">
+        <v>2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4">
         <v>1.629206092387903</v>
@@ -1848,25 +2807,41 @@
       <c r="M16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="25" customHeight="1">
+      <c r="N16" s="4"/>
+      <c r="O16" s="5">
+        <v>2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1.629206092387903</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>1.629206092387903</v>
+      </c>
+      <c r="R16" s="5">
+        <v>2</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4">
-        <v>1.679205609867495</v>
+        <v>1.44348199297383</v>
       </c>
       <c r="C17" s="4">
-        <v>1.679205609867495</v>
+        <v>1.44348199297383</v>
       </c>
       <c r="D17" s="4">
-        <v>1.696029855320376</v>
+        <v>1.456229995979811</v>
       </c>
       <c r="E17" s="4">
-        <v>84.18367346938776</v>
+        <v>84.84693877551021</v>
       </c>
       <c r="F17" s="4">
-        <v>89.81543624161074</v>
+        <v>90.30201342281879</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1889,25 +2864,41 @@
       <c r="M17" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="25" customHeight="1">
+      <c r="N17" s="4"/>
+      <c r="O17" s="5">
+        <v>2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1.44348199297383</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>1.44348199297383</v>
+      </c>
+      <c r="R17" s="5">
+        <v>2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4">
-        <v>1.44348199297383</v>
+        <v>1.600154345833289</v>
       </c>
       <c r="C18" s="4">
-        <v>1.44348199297383</v>
+        <v>1.600154345833289</v>
       </c>
       <c r="D18" s="4">
-        <v>1.456229995979811</v>
+        <v>1.588674491249549</v>
       </c>
       <c r="E18" s="4">
-        <v>84.84693877551021</v>
+        <v>82.80612244897959</v>
       </c>
       <c r="F18" s="4">
-        <v>90.30201342281879</v>
+        <v>89.16107382550335</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -1930,9 +2921,25 @@
       <c r="M18" s="5">
         <v>0</v>
       </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1.600154345833289</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>1.600154345833289</v>
+      </c>
+      <c r="R18" s="5">
+        <v>2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1943,14 +2950,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1961,9 +2969,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1997,8 +3011,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2020,10 +3042,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>0.5991329896293586</v>
@@ -2061,10 +3101,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6304902102287997</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1851961600057826</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1870040749651783</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4">
         <v>0.3891731091099636</v>
@@ -2102,10 +3160,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4048135104644294</v>
+      </c>
+      <c r="O4" s="5">
+        <v>26</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2447629811958505</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2371705533166854</v>
+      </c>
+      <c r="R4" s="5">
+        <v>26</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
         <v>0.3769809359569494</v>
@@ -2143,10 +3219,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3831402272323127</v>
+      </c>
+      <c r="O5" s="5">
+        <v>18</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2408318814476925</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1989016081063676</v>
+      </c>
+      <c r="R5" s="5">
+        <v>18</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
         <v>1.399347694821578</v>
@@ -2184,10 +3278,28 @@
       <c r="M6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-1.382991888710551</v>
+      </c>
+      <c r="O6" s="5">
+        <v>14</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.323424538819312</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3290022136160197</v>
+      </c>
+      <c r="R6" s="5">
+        <v>14</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4">
         <v>1.299847249525919</v>
@@ -2225,10 +3337,28 @@
       <c r="M7" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.299847249525919</v>
+      </c>
+      <c r="O7" s="5">
+        <v>10</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4926099833966873</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4926099833966873</v>
+      </c>
+      <c r="R7" s="5">
+        <v>10</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
         <v>1.495780920030484</v>
@@ -2266,78 +3396,114 @@
       <c r="M8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-1.495780920030484</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2286716283158512</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2286716283158512</v>
+      </c>
+      <c r="R8" s="5">
+        <v>8</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4">
-        <v>1.760440578121234</v>
+        <v>1.80410366475553</v>
       </c>
       <c r="C9" s="4">
-        <v>1.640803976689009</v>
+        <v>1.757018751982417</v>
       </c>
       <c r="D9" s="4">
-        <v>1.64436601604848</v>
+        <v>1.799605421423621</v>
       </c>
       <c r="E9" s="4">
-        <v>73.60544217687075</v>
+        <v>75.35714285714286</v>
       </c>
       <c r="F9" s="4">
-        <v>77.80620805369128</v>
+        <v>83.8660514541387</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
       </c>
       <c r="H9" s="5">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
+        <v>-1.80410366475553</v>
+      </c>
+      <c r="O9" s="5">
+        <v>8</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1881814804000896</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1881814804000896</v>
+      </c>
+      <c r="R9" s="5">
+        <v>8</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.883531121678061</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.836666058556148</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.838716058201499</v>
+      </c>
+      <c r="E10" s="4">
+        <v>75.85034013605443</v>
+      </c>
+      <c r="F10" s="4">
+        <v>82.00503355704693</v>
+      </c>
+      <c r="G10" s="5">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5">
         <v>6</v>
       </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>2</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.2490891342722534</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0.2490891342722534</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.1889542465769409</v>
-      </c>
-      <c r="E10" s="4">
-        <v>80.02551020408163</v>
-      </c>
-      <c r="F10" s="4">
-        <v>87.84675615212527</v>
-      </c>
-      <c r="G10" s="5">
-        <v>8</v>
-      </c>
-      <c r="H10" s="5">
-        <v>8</v>
-      </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -2346,12 +3512,30 @@
         <v>0</v>
       </c>
       <c r="M10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-1.883531121678061</v>
+      </c>
+      <c r="O10" s="5">
+        <v>8</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1191684838688616</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1191684838688616</v>
+      </c>
+      <c r="R10" s="5">
+        <v>8</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4">
         <v>1.775469179182437</v>
@@ -2389,25 +3573,43 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-1.749240974255372</v>
+      </c>
+      <c r="O11" s="5">
+        <v>7</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.1050492546901296</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.09008119972921642</v>
+      </c>
+      <c r="R11" s="5">
+        <v>7</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4">
-        <v>1.883531121678061</v>
+        <v>1.760440578121234</v>
       </c>
       <c r="C12" s="4">
-        <v>1.836666058556148</v>
+        <v>1.640803976689009</v>
       </c>
       <c r="D12" s="4">
-        <v>1.838716058201499</v>
+        <v>1.64436601604848</v>
       </c>
       <c r="E12" s="4">
-        <v>75.85034013605443</v>
+        <v>73.60544217687075</v>
       </c>
       <c r="F12" s="4">
-        <v>82.00503355704693</v>
+        <v>77.80620805369128</v>
       </c>
       <c r="G12" s="5">
         <v>8</v>
@@ -2430,25 +3632,43 @@
       <c r="M12" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-1.760440578121234</v>
+      </c>
+      <c r="O12" s="5">
+        <v>8</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2484019745761543</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2484019745761543</v>
+      </c>
+      <c r="R12" s="5">
+        <v>8</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4">
-        <v>1.80410366475553</v>
+        <v>0.4300648868520511</v>
       </c>
       <c r="C13" s="4">
-        <v>1.757018751982417</v>
+        <v>0.4155202854349876</v>
       </c>
       <c r="D13" s="4">
-        <v>1.799605421423621</v>
+        <v>0.3613245189626468</v>
       </c>
       <c r="E13" s="4">
-        <v>75.35714285714286</v>
+        <v>73.76700680272108</v>
       </c>
       <c r="F13" s="4">
-        <v>83.8660514541387</v>
+        <v>78.02013422818786</v>
       </c>
       <c r="G13" s="5">
         <v>8</v>
@@ -2457,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="I13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -2469,36 +3689,54 @@
         <v>0</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>-0.4069309936063031</v>
+      </c>
+      <c r="O13" s="5">
+        <v>7</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.1568663764563618</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1614264154979574</v>
+      </c>
+      <c r="R13" s="5">
+        <v>7</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4">
-        <v>0.4300648868520511</v>
+        <v>0.2490891342722534</v>
       </c>
       <c r="C14" s="4">
-        <v>0.4155202854349876</v>
+        <v>0.2490891342722534</v>
       </c>
       <c r="D14" s="4">
-        <v>0.3613245189626468</v>
+        <v>0.1889542465769409</v>
       </c>
       <c r="E14" s="4">
-        <v>73.76700680272108</v>
+        <v>80.02551020408163</v>
       </c>
       <c r="F14" s="4">
-        <v>78.02013422818786</v>
+        <v>87.84675615212527</v>
       </c>
       <c r="G14" s="5">
         <v>8</v>
       </c>
       <c r="H14" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5">
         <v>0</v>
@@ -2512,25 +3750,43 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>0.2254197946667773</v>
+      </c>
+      <c r="O14" s="5">
+        <v>8</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.1689293803383407</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.1689293803383407</v>
+      </c>
+      <c r="R14" s="5">
+        <v>8</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4">
-        <v>0.8652800973286503</v>
+        <v>1.617706491062563</v>
       </c>
       <c r="C15" s="4">
-        <v>0.8652800973286503</v>
+        <v>1.617706491062563</v>
       </c>
       <c r="D15" s="4">
-        <v>0.895301764809119</v>
+        <v>1.606591416904848</v>
       </c>
       <c r="E15" s="4">
-        <v>69.93197278911565</v>
+        <v>70.95238095238096</v>
       </c>
       <c r="F15" s="4">
-        <v>78.86465324384788</v>
+        <v>77.27069351230423</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -2553,17 +3809,31 @@
       <c r="M15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4"/>
+      <c r="O15" s="5">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1.617706491062563</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>1.617706491062563</v>
+      </c>
+      <c r="R15" s="5">
+        <v>2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4">
         <v>1.972141892940272</v>
       </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
+      <c r="C16" s="4"/>
       <c r="D16" s="4">
         <v>1.839535386592615</v>
       </c>
@@ -2594,25 +3864,39 @@
       <c r="M16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="25" customHeight="1">
+      <c r="N16" s="4"/>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1.972141892940272</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4">
-        <v>1.617706491062563</v>
+        <v>0.9146526568074478</v>
       </c>
       <c r="C17" s="4">
-        <v>1.617706491062563</v>
+        <v>0.9146526568074478</v>
       </c>
       <c r="D17" s="4">
-        <v>1.606591416904848</v>
+        <v>0.9841602556844009</v>
       </c>
       <c r="E17" s="4">
-        <v>70.95238095238096</v>
+        <v>73.62244897959184</v>
       </c>
       <c r="F17" s="4">
-        <v>77.27069351230423</v>
+        <v>85.16778523489933</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -2635,25 +3919,41 @@
       <c r="M17" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="25" customHeight="1">
+      <c r="N17" s="4"/>
+      <c r="O17" s="5">
+        <v>2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0.9146526568074478</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0.9146526568074478</v>
+      </c>
+      <c r="R17" s="5">
+        <v>2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4">
-        <v>0.9146526568074478</v>
+        <v>0.8652800973286503</v>
       </c>
       <c r="C18" s="4">
-        <v>0.9146526568074478</v>
+        <v>0.8652800973286503</v>
       </c>
       <c r="D18" s="4">
-        <v>0.9841602556844009</v>
+        <v>0.895301764809119</v>
       </c>
       <c r="E18" s="4">
-        <v>73.62244897959184</v>
+        <v>69.93197278911565</v>
       </c>
       <c r="F18" s="4">
-        <v>85.16778523489933</v>
+        <v>78.86465324384788</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2676,9 +3976,25 @@
       <c r="M18" s="5">
         <v>0</v>
       </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.8652800973286503</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.8652800973286503</v>
+      </c>
+      <c r="R18" s="5">
+        <v>2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2689,14 +4005,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2707,9 +4024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2743,8 +4066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2766,10 +4097,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>0.3084558700571624</v>
@@ -2807,10 +4156,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1977969175998253</v>
+      </c>
+      <c r="O3" s="5">
+        <v>27</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2220999552965355</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2346134498864593</v>
+      </c>
+      <c r="R3" s="5">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4">
         <v>0.5191845383637234</v>
@@ -2848,10 +4215,28 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1104785695201826</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5783522458249796</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3277019581814784</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
         <v>0.278073868787694</v>
@@ -2889,10 +4274,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.29971220998737</v>
+      </c>
+      <c r="O5" s="5">
+        <v>18</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1037859932514057</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09833992952621043</v>
+      </c>
+      <c r="R5" s="5">
+        <v>18</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
         <v>0.7540701335742294</v>
@@ -2930,10 +4333,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.7540701335742294</v>
+      </c>
+      <c r="O6" s="5">
+        <v>15</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2471065215479919</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2471065215479919</v>
+      </c>
+      <c r="R6" s="5">
+        <v>15</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4">
         <v>0.7841958752156643</v>
@@ -2971,10 +4392,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.7841958752156643</v>
+      </c>
+      <c r="O7" s="5">
+        <v>10</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2586681204006891</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2586681204006891</v>
+      </c>
+      <c r="R7" s="5">
+        <v>10</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
         <v>0.7436087051200957</v>
@@ -3012,25 +4451,43 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.7436087051200957</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1338633383356864</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1338633383356864</v>
+      </c>
+      <c r="R8" s="5">
+        <v>8</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4">
-        <v>0.9082165159243232</v>
+        <v>0.9338870976862381</v>
       </c>
       <c r="C9" s="4">
-        <v>0.9082165159243232</v>
+        <v>0.9338870976862381</v>
       </c>
       <c r="D9" s="4">
-        <v>0.8713014231952911</v>
+        <v>0.9855031275001238</v>
       </c>
       <c r="E9" s="4">
-        <v>79.1454081632653</v>
+        <v>82.53826530612245</v>
       </c>
       <c r="F9" s="4">
-        <v>82.84395973154362</v>
+        <v>90.16778523489933</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
@@ -3053,51 +4510,87 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.9338870976862381</v>
+      </c>
+      <c r="O9" s="5">
+        <v>8</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.09582776400748116</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.09582776400748116</v>
+      </c>
+      <c r="R9" s="5">
+        <v>8</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" s="4">
-        <v>0.4918107644398333</v>
+        <v>1.022221377260394</v>
       </c>
       <c r="C10" s="4">
-        <v>0.2763123825092667</v>
+        <v>1.022221377260394</v>
       </c>
       <c r="D10" s="4">
-        <v>1.052577374756765</v>
+        <v>1.01584416269452</v>
       </c>
       <c r="E10" s="4">
-        <v>80.87585034013607</v>
+        <v>81.84948979591837</v>
       </c>
       <c r="F10" s="4">
-        <v>84.35822147651007</v>
+        <v>87.86493288590604</v>
       </c>
       <c r="G10" s="5">
         <v>8</v>
       </c>
       <c r="H10" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-1.022221377260394</v>
+      </c>
+      <c r="O10" s="5">
+        <v>8</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1073706788722575</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1073706788722575</v>
+      </c>
+      <c r="R10" s="5">
+        <v>8</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4">
         <v>0.9875981751001746</v>
@@ -3135,25 +4628,43 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-0.9875981751001746</v>
+      </c>
+      <c r="O11" s="5">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.09012563728742862</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.09012563728742862</v>
+      </c>
+      <c r="R11" s="5">
+        <v>8</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4">
-        <v>1.022221377260394</v>
+        <v>0.9082165159243232</v>
       </c>
       <c r="C12" s="4">
-        <v>1.022221377260394</v>
+        <v>0.9082165159243232</v>
       </c>
       <c r="D12" s="4">
-        <v>1.01584416269452</v>
+        <v>0.8713014231952911</v>
       </c>
       <c r="E12" s="4">
-        <v>81.84948979591837</v>
+        <v>79.1454081632653</v>
       </c>
       <c r="F12" s="4">
-        <v>87.86493288590604</v>
+        <v>82.84395973154362</v>
       </c>
       <c r="G12" s="5">
         <v>8</v>
@@ -3176,25 +4687,43 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.9082165159243232</v>
+      </c>
+      <c r="O12" s="5">
+        <v>8</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2004098317274838</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2004098317274838</v>
+      </c>
+      <c r="R12" s="5">
+        <v>8</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4">
-        <v>0.9338870976862381</v>
+        <v>0.545983733400135</v>
       </c>
       <c r="C13" s="4">
-        <v>0.9338870976862381</v>
+        <v>0.545983733400135</v>
       </c>
       <c r="D13" s="4">
-        <v>0.9855031275001238</v>
+        <v>0.5760671866828488</v>
       </c>
       <c r="E13" s="4">
-        <v>82.53826530612245</v>
+        <v>81.05867346938776</v>
       </c>
       <c r="F13" s="4">
-        <v>90.16778523489933</v>
+        <v>86.85822147651007</v>
       </c>
       <c r="G13" s="5">
         <v>8</v>
@@ -3217,66 +4746,102 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+      <c r="N13" s="4">
+        <v>-0.3820403287245426</v>
+      </c>
+      <c r="O13" s="5">
+        <v>8</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.259453486856728</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.259453486856728</v>
+      </c>
+      <c r="R13" s="5">
+        <v>8</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4">
-        <v>0.545983733400135</v>
+        <v>0.4918107644398333</v>
       </c>
       <c r="C14" s="4">
-        <v>0.545983733400135</v>
+        <v>0.2763123825092667</v>
       </c>
       <c r="D14" s="4">
-        <v>0.5760671866828488</v>
+        <v>1.052577374756765</v>
       </c>
       <c r="E14" s="4">
-        <v>81.05867346938776</v>
+        <v>80.87585034013607</v>
       </c>
       <c r="F14" s="4">
-        <v>86.85822147651007</v>
+        <v>84.35822147651007</v>
       </c>
       <c r="G14" s="5">
         <v>8</v>
       </c>
       <c r="H14" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
       </c>
       <c r="J14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>-0.2763123825092667</v>
+      </c>
+      <c r="O14" s="5">
+        <v>7</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.3639937988262837</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.09076265287817199</v>
+      </c>
+      <c r="R14" s="5">
+        <v>7</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4">
-        <v>0.7814100291361683</v>
+        <v>0.9217428028678114</v>
       </c>
       <c r="C15" s="4">
-        <v>0.7814100291361683</v>
+        <v>0.9217428028678114</v>
       </c>
       <c r="D15" s="4">
-        <v>0.8331781830420368</v>
+        <v>0.9489493131732161</v>
       </c>
       <c r="E15" s="4">
-        <v>82.24489795918367</v>
+        <v>80.61224489795919</v>
       </c>
       <c r="F15" s="4">
-        <v>89.44630872483222</v>
+        <v>87.14765100671141</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -3299,10 +4864,26 @@
       <c r="M15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4"/>
+      <c r="O15" s="5">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.9217428028678114</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.9217428028678114</v>
+      </c>
+      <c r="R15" s="5">
+        <v>2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4">
         <v>1.09872254851507</v>
@@ -3340,25 +4921,41 @@
       <c r="M16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="25" customHeight="1">
+      <c r="N16" s="4"/>
+      <c r="O16" s="5">
+        <v>2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1.09872254851507</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>1.09872254851507</v>
+      </c>
+      <c r="R16" s="5">
+        <v>2</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4">
-        <v>0.9217428028678114</v>
+        <v>0.8751146533031715</v>
       </c>
       <c r="C17" s="4">
-        <v>0.9217428028678114</v>
+        <v>0.8751146533031715</v>
       </c>
       <c r="D17" s="4">
-        <v>0.9489493131732161</v>
+        <v>0.9588280655880226</v>
       </c>
       <c r="E17" s="4">
-        <v>80.61224489795919</v>
+        <v>82.90816326530613</v>
       </c>
       <c r="F17" s="4">
-        <v>87.14765100671141</v>
+        <v>90.67114093959732</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -3381,25 +4978,41 @@
       <c r="M17" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="25" customHeight="1">
+      <c r="N17" s="4"/>
+      <c r="O17" s="5">
+        <v>2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0.8751146533031715</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0.8751146533031715</v>
+      </c>
+      <c r="R17" s="5">
+        <v>2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4">
-        <v>0.8751146533031715</v>
+        <v>0.7814100291361683</v>
       </c>
       <c r="C18" s="4">
-        <v>0.8751146533031715</v>
+        <v>0.7814100291361683</v>
       </c>
       <c r="D18" s="4">
-        <v>0.9588280655880226</v>
+        <v>0.8331781830420368</v>
       </c>
       <c r="E18" s="4">
-        <v>82.90816326530613</v>
+        <v>82.24489795918367</v>
       </c>
       <c r="F18" s="4">
-        <v>90.67114093959732</v>
+        <v>89.44630872483222</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -3422,9 +5035,25 @@
       <c r="M18" s="5">
         <v>0</v>
       </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.7814100291361683</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.7814100291361683</v>
+      </c>
+      <c r="R18" s="5">
+        <v>2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3435,14 +5064,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3453,9 +5083,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -3489,8 +5125,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3512,10 +5156,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>0.3122940360573921</v>
@@ -3553,10 +5215,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.04301374724491325</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3059258108656649</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3133880323930498</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4">
         <v>0.5080004982767908</v>
@@ -3594,10 +5274,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4823371187328576</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.635022682237478</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4046368368272591</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
         <v>0.3699316055109583</v>
@@ -3635,10 +5333,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4076491273414528</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.140119649526501</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1194691489786742</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
         <v>0.9813708420639159</v>
@@ -3676,10 +5392,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.9813708420639159</v>
+      </c>
+      <c r="O6" s="5">
+        <v>10</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3343519172893138</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3343519172893138</v>
+      </c>
+      <c r="R6" s="5">
+        <v>10</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4">
         <v>0.7584843255841406</v>
@@ -3717,10 +5451,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.7584843255841406</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3040231365058571</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3040231365058571</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
         <v>1.074498696929368</v>
@@ -3758,31 +5510,47 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>4</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.074498696929368</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1.074498696929368</v>
+      </c>
+      <c r="R8" s="5">
+        <v>4</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4">
-        <v>1.067829898577475</v>
+        <v>1.371387945780953</v>
       </c>
       <c r="C9" s="4">
-        <v>1.067829898577475</v>
+        <v>1.371387945780953</v>
       </c>
       <c r="D9" s="4">
-        <v>0.8884597813899745</v>
+        <v>1.347875582347115</v>
       </c>
       <c r="E9" s="4">
-        <v>77.08163265306122</v>
+        <v>83.18877551020408</v>
       </c>
       <c r="F9" s="4">
-        <v>78.24832214765101</v>
+        <v>89.79865771812081</v>
       </c>
       <c r="G9" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
@@ -3799,34 +5567,50 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>4</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.371387945780953</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>1.371387945780953</v>
+      </c>
+      <c r="R9" s="5">
+        <v>4</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" s="4">
-        <v>0.6452466979302699</v>
+        <v>1.28700397539651</v>
       </c>
       <c r="C10" s="4">
-        <v>0.3152168935102964</v>
+        <v>1.28700397539651</v>
       </c>
       <c r="D10" s="4">
-        <v>1.059627057579928</v>
+        <v>1.2068043522886</v>
       </c>
       <c r="E10" s="4">
-        <v>82.14285714285714</v>
+        <v>82.04081632653062</v>
       </c>
       <c r="F10" s="4">
-        <v>86.58389261744966</v>
+        <v>85.24832214765101</v>
       </c>
       <c r="G10" s="5">
         <v>5</v>
       </c>
       <c r="H10" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5">
         <v>0</v>
@@ -3840,10 +5624,28 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-1.28700397539651</v>
+      </c>
+      <c r="O10" s="5">
+        <v>5</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.2374246492848033</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.2374246492848033</v>
+      </c>
+      <c r="R10" s="5">
+        <v>5</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4">
         <v>1.114099654718302</v>
@@ -3881,25 +5683,43 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-1.114099654718302</v>
+      </c>
+      <c r="O11" s="5">
+        <v>5</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.1267061194084818</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1267061194084818</v>
+      </c>
+      <c r="R11" s="5">
+        <v>5</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4">
-        <v>1.28700397539651</v>
+        <v>1.067829898577475</v>
       </c>
       <c r="C12" s="4">
-        <v>1.28700397539651</v>
+        <v>1.067829898577475</v>
       </c>
       <c r="D12" s="4">
-        <v>1.2068043522886</v>
+        <v>0.8884597813899745</v>
       </c>
       <c r="E12" s="4">
-        <v>82.04081632653062</v>
+        <v>77.08163265306122</v>
       </c>
       <c r="F12" s="4">
-        <v>85.24832214765101</v>
+        <v>78.24832214765101</v>
       </c>
       <c r="G12" s="5">
         <v>5</v>
@@ -3922,34 +5742,52 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-1.067829898577475</v>
+      </c>
+      <c r="O12" s="5">
+        <v>5</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.3296979836182436</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.3296979836182436</v>
+      </c>
+      <c r="R12" s="5">
+        <v>5</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4">
-        <v>1.371387945780953</v>
+        <v>0.7581411806197138</v>
       </c>
       <c r="C13" s="4">
-        <v>1.371387945780953</v>
+        <v>0.5692788738548794</v>
       </c>
       <c r="D13" s="4">
-        <v>1.347875582347115</v>
+        <v>1.16758684788656</v>
       </c>
       <c r="E13" s="4">
-        <v>83.18877551020408</v>
+        <v>74.79591836734694</v>
       </c>
       <c r="F13" s="4">
-        <v>89.79865771812081</v>
+        <v>73.33557046979867</v>
       </c>
       <c r="G13" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="5">
         <v>0</v>
@@ -3963,34 +5801,50 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+      <c r="N13" s="4"/>
+      <c r="O13" s="5">
+        <v>3</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.7581411806197138</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.5692788738548794</v>
+      </c>
+      <c r="R13" s="5">
+        <v>3</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4">
-        <v>0.7581411806197138</v>
+        <v>0.6452466979302699</v>
       </c>
       <c r="C14" s="4">
-        <v>0.5692788738548794</v>
+        <v>0.3152168935102964</v>
       </c>
       <c r="D14" s="4">
-        <v>1.16758684788656</v>
+        <v>1.059627057579928</v>
       </c>
       <c r="E14" s="4">
-        <v>74.79591836734694</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="F14" s="4">
-        <v>73.33557046979867</v>
+        <v>86.58389261744966</v>
       </c>
       <c r="G14" s="5">
         <v>5</v>
       </c>
       <c r="H14" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5">
         <v>0</v>
@@ -4004,9 +5858,25 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
+      <c r="N14" s="4"/>
+      <c r="O14" s="5">
+        <v>4</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.6452466979302699</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.3152168935102964</v>
+      </c>
+      <c r="R14" s="5">
+        <v>4</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4017,14 +5887,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4035,9 +5906,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -4071,8 +5948,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4094,10 +5979,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>0.267790599640543</v>
@@ -4135,10 +6038,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1282490795581662</v>
+      </c>
+      <c r="O3" s="5">
+        <v>28</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2297002067288433</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2168239353113269</v>
+      </c>
+      <c r="R3" s="5">
+        <v>28</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4">
         <v>0.1782100412023997</v>
@@ -4176,10 +6097,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.0182629717302122</v>
+      </c>
+      <c r="O4" s="5">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1734300204422115</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1421124570702214</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
         <v>0.1971298584180431</v>
@@ -4217,10 +6156,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.1841980677440412</v>
+      </c>
+      <c r="O5" s="5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09953570787222582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09009820710661151</v>
+      </c>
+      <c r="R5" s="5">
+        <v>19</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
         <v>0.5903995848987134</v>
@@ -4258,10 +6215,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4103203168230823</v>
+      </c>
+      <c r="O6" s="5">
+        <v>15</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3003492603363602</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3003492603363602</v>
+      </c>
+      <c r="R6" s="5">
+        <v>15</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4">
         <v>0.4786339970143654</v>
@@ -4299,10 +6274,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.403405546631349</v>
+      </c>
+      <c r="O7" s="5">
+        <v>10</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1971213667192278</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1971213667192278</v>
+      </c>
+      <c r="R7" s="5">
+        <v>10</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
         <v>0.7048284337104416</v>
@@ -4340,25 +6333,43 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.4147295765462073</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.4097409922221952</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.4097409922221952</v>
+      </c>
+      <c r="R8" s="5">
+        <v>8</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4">
-        <v>0.5127852012141663</v>
+        <v>0.683229189144356</v>
       </c>
       <c r="C9" s="4">
-        <v>0.5127852012141663</v>
+        <v>0.683229189144356</v>
       </c>
       <c r="D9" s="4">
-        <v>0.4854861870315066</v>
+        <v>0.7322972115020374</v>
       </c>
       <c r="E9" s="4">
-        <v>78.12074829931974</v>
+        <v>79.60034013605441</v>
       </c>
       <c r="F9" s="4">
-        <v>82.12667785234899</v>
+        <v>88.86325503355705</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
@@ -4381,25 +6392,43 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.5362153797759053</v>
+      </c>
+      <c r="O9" s="5">
+        <v>8</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.2958781729297502</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.2958781729297502</v>
+      </c>
+      <c r="R9" s="5">
+        <v>8</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" s="4">
-        <v>0.2610702867798302</v>
+        <v>0.6393366816994424</v>
       </c>
       <c r="C10" s="4">
-        <v>0.2610702867798302</v>
+        <v>0.6393366816994424</v>
       </c>
       <c r="D10" s="4">
-        <v>0.2746129793419634</v>
+        <v>0.6395511249738872</v>
       </c>
       <c r="E10" s="4">
-        <v>82.23639455782312</v>
+        <v>80.65901360544217</v>
       </c>
       <c r="F10" s="4">
-        <v>89.09395973154362</v>
+        <v>87.39093959731544</v>
       </c>
       <c r="G10" s="5">
         <v>8</v>
@@ -4422,10 +6451,28 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.6393366816994424</v>
+      </c>
+      <c r="O10" s="5">
+        <v>8</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1653649305885756</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1653649305885756</v>
+      </c>
+      <c r="R10" s="5">
+        <v>8</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4">
         <v>0.6954530147458589</v>
@@ -4463,25 +6510,43 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-0.6954530147458589</v>
+      </c>
+      <c r="O11" s="5">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.05381761811563945</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.05381761811563945</v>
+      </c>
+      <c r="R11" s="5">
+        <v>8</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4">
-        <v>0.6393366816994424</v>
+        <v>0.5127852012141663</v>
       </c>
       <c r="C12" s="4">
-        <v>0.6393366816994424</v>
+        <v>0.5127852012141663</v>
       </c>
       <c r="D12" s="4">
-        <v>0.6395511249738872</v>
+        <v>0.4854861870315066</v>
       </c>
       <c r="E12" s="4">
-        <v>80.65901360544217</v>
+        <v>78.12074829931974</v>
       </c>
       <c r="F12" s="4">
-        <v>87.39093959731544</v>
+        <v>82.12667785234899</v>
       </c>
       <c r="G12" s="5">
         <v>8</v>
@@ -4504,25 +6569,43 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.4810800382709477</v>
+      </c>
+      <c r="O12" s="5">
+        <v>8</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2035895044078919</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2035895044078919</v>
+      </c>
+      <c r="R12" s="5">
+        <v>8</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4">
-        <v>0.683229189144356</v>
+        <v>0.2816853819823777</v>
       </c>
       <c r="C13" s="4">
-        <v>0.683229189144356</v>
+        <v>0.2816853819823777</v>
       </c>
       <c r="D13" s="4">
-        <v>0.7322972115020374</v>
+        <v>0.2785458822220521</v>
       </c>
       <c r="E13" s="4">
-        <v>79.60034013605441</v>
+        <v>80.64625850340137</v>
       </c>
       <c r="F13" s="4">
-        <v>88.86325503355705</v>
+        <v>87.51677852348993</v>
       </c>
       <c r="G13" s="5">
         <v>8</v>
@@ -4545,25 +6628,43 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+      <c r="N13" s="4">
+        <v>-0.2816853819823777</v>
+      </c>
+      <c r="O13" s="5">
+        <v>8</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.1074467867570306</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1074467867570306</v>
+      </c>
+      <c r="R13" s="5">
+        <v>8</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4">
-        <v>0.2816853819823777</v>
+        <v>0.2610702867798302</v>
       </c>
       <c r="C14" s="4">
-        <v>0.2816853819823777</v>
+        <v>0.2610702867798302</v>
       </c>
       <c r="D14" s="4">
-        <v>0.2785458822220521</v>
+        <v>0.2746129793419634</v>
       </c>
       <c r="E14" s="4">
-        <v>80.64625850340137</v>
+        <v>82.23639455782312</v>
       </c>
       <c r="F14" s="4">
-        <v>87.51677852348993</v>
+        <v>89.09395973154362</v>
       </c>
       <c r="G14" s="5">
         <v>8</v>
@@ -4586,25 +6687,43 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>-0.2610702867798302</v>
+      </c>
+      <c r="O14" s="5">
+        <v>8</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.09587444335795325</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.09587444335795325</v>
+      </c>
+      <c r="R14" s="5">
+        <v>8</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4">
-        <v>0.3933631510421165</v>
+        <v>0.3993034309997734</v>
       </c>
       <c r="C15" s="4">
-        <v>0.3933631510421165</v>
+        <v>0.3993034309997734</v>
       </c>
       <c r="D15" s="4">
-        <v>0.4311508188018394</v>
+        <v>0.4198648207970725</v>
       </c>
       <c r="E15" s="4">
-        <v>89.16666666666666</v>
+        <v>84.69387755102041</v>
       </c>
       <c r="F15" s="4">
-        <v>94.01006711409396</v>
+        <v>85.52013422818791</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -4627,10 +6746,26 @@
       <c r="M15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4"/>
+      <c r="O15" s="5">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.3993034309997734</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.3993034309997734</v>
+      </c>
+      <c r="R15" s="5">
+        <v>2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4">
         <v>0.4688184002102602</v>
@@ -4668,25 +6803,41 @@
       <c r="M16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="25" customHeight="1">
+      <c r="N16" s="4"/>
+      <c r="O16" s="5">
+        <v>2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.4688184002102602</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.4688184002102602</v>
+      </c>
+      <c r="R16" s="5">
+        <v>2</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4">
-        <v>0.3993034309997734</v>
+        <v>0.4644644833424847</v>
       </c>
       <c r="C17" s="4">
-        <v>0.3993034309997734</v>
+        <v>0.4644644833424847</v>
       </c>
       <c r="D17" s="4">
-        <v>0.4198648207970725</v>
+        <v>0.5112641993057885</v>
       </c>
       <c r="E17" s="4">
-        <v>84.69387755102041</v>
+        <v>90.66326530612245</v>
       </c>
       <c r="F17" s="4">
-        <v>85.52013422818791</v>
+        <v>94.14429530201342</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -4709,25 +6860,41 @@
       <c r="M17" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="25" customHeight="1">
+      <c r="N17" s="4"/>
+      <c r="O17" s="5">
+        <v>2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0.4644644833424847</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0.4644644833424847</v>
+      </c>
+      <c r="R17" s="5">
+        <v>2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4">
-        <v>0.4644644833424847</v>
+        <v>0.3933631510421165</v>
       </c>
       <c r="C18" s="4">
-        <v>0.4644644833424847</v>
+        <v>0.3933631510421165</v>
       </c>
       <c r="D18" s="4">
-        <v>0.5112641993057885</v>
+        <v>0.4311508188018394</v>
       </c>
       <c r="E18" s="4">
-        <v>90.66326530612245</v>
+        <v>89.16666666666666</v>
       </c>
       <c r="F18" s="4">
-        <v>94.14429530201342</v>
+        <v>94.01006711409396</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -4750,9 +6917,25 @@
       <c r="M18" s="5">
         <v>0</v>
       </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.3933631510421165</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.3933631510421165</v>
+      </c>
+      <c r="R18" s="5">
+        <v>2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4763,6 +6946,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/TangFrom2020.xlsx
+++ b/public/downloads/TangFrom2020.xlsx
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.9013150146781537</v>
+        <v>0.8947392720368311</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2054240254561325</v>
+        <v>0.1995168871537724</v>
       </c>
       <c r="J3" s="4">
-        <v>2.920345950633251</v>
+        <v>2.916970911812721</v>
       </c>
       <c r="K3" s="4">
         <v>78.26390556222488</v>
@@ -1070,13 +1070,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2831289685130179</v>
+        <v>0.2799444078793278</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2628259692953012</v>
+        <v>0.2586486963453258</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3056527187606733</v>
+        <v>0.305130353918781</v>
       </c>
       <c r="K4" s="4">
         <v>73.72488995598252</v>
@@ -1120,13 +1120,13 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2883404043000056</v>
+        <v>0.2697066042464832</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2373130158865073</v>
+        <v>0.2171185690897404</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3823950343759309</v>
+        <v>0.3674865947852274</v>
       </c>
       <c r="K5" s="4">
         <v>80.71488595438174</v>
@@ -1170,13 +1170,13 @@
         <v>2</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4464386417153018</v>
+        <v>0.4158701687651774</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3800512299980651</v>
+        <v>0.3345915152668578</v>
       </c>
       <c r="J6" s="4">
-        <v>0.5075730250506801</v>
+        <v>0.4894072897751903</v>
       </c>
       <c r="K6" s="4">
         <v>80.25408163265305</v>
@@ -1220,13 +1220,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2044034332036722</v>
+        <v>0.1920754301517672</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1989532938793529</v>
+        <v>0.1855734824401863</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1882047353312603</v>
+        <v>0.175773244498812</v>
       </c>
       <c r="K7" s="4">
         <v>79.49319727891152</v>
@@ -2043,16 +2043,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7201155342922902</v>
+        <v>-0.7653803709326894</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3709392188317555</v>
+        <v>0.3765000920805417</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1122325583578079</v>
+        <v>0.1099851786707404</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -2102,16 +2102,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1093223060000706</v>
+        <v>0.182898815452063</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>2.295690978990532</v>
+        <v>2.272775454480844</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1647882791108143</v>
+        <v>0.1556893868581193</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -2161,16 +2161,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3973663742923664</v>
+        <v>-0.3527150929439813</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1587239331253748</v>
+        <v>0.1460488951713408</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1048738675060679</v>
+        <v>0.09761874229340772</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -2220,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.464221280582933</v>
+        <v>-1.462727501850168</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>1.350143300163836</v>
+        <v>1.349844544417283</v>
       </c>
       <c r="Q6" s="4">
         <v>0.1350254528315418</v>
@@ -2279,16 +2279,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.437545283056352</v>
+        <v>-1.414476095113059</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>1.302248032531133</v>
+        <v>1.29682013976053</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09981280796500869</v>
+        <v>0.09302794200175413</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -2338,16 +2338,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.539798711778531</v>
+        <v>-1.474149047357059</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1693051140152875</v>
+        <v>0.1575078895230035</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1693051140152875</v>
+        <v>0.1575078895230035</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.773777894377417</v>
+        <v>-1.723579897952732</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
@@ -2456,16 +2456,16 @@
         <v>6</v>
       </c>
       <c r="N10" s="4">
-        <v>-2.071528701252646</v>
+        <v>-2.111140986184182</v>
       </c>
       <c r="O10" s="5">
         <v>8</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1073998996394039</v>
+        <v>0.09244376922197262</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1073998996394039</v>
+        <v>0.09244376922197262</v>
       </c>
       <c r="R10" s="5">
         <v>8</v>
@@ -2515,16 +2515,16 @@
         <v>2</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.934663052587894</v>
+        <v>-1.948283303761855</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.06748076675444281</v>
+        <v>0.06585548653401929</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.06748076675444281</v>
+        <v>0.06585548653401929</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-1.498088846462148</v>
+        <v>-1.471553412153298</v>
       </c>
       <c r="O12" s="5">
         <v>6</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.7983215883276509</v>
+        <v>-0.8431137167208362</v>
       </c>
       <c r="O13" s="5">
         <v>7</v>
@@ -2642,7 +2642,7 @@
         <v>0.9556303868503164</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1144986723823478</v>
+        <v>0.108099796897607</v>
       </c>
       <c r="R13" s="5">
         <v>7</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.6855933308501595</v>
+        <v>-0.7427756467513973</v>
       </c>
       <c r="O14" s="5">
         <v>7</v>
       </c>
       <c r="P14" s="4">
-        <v>1.066424014914576</v>
+        <v>1.055925458223101</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1168116201793333</v>
+        <v>0.09664436740318447</v>
       </c>
       <c r="R14" s="5">
         <v>7</v>
@@ -3102,16 +3102,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6304902102287997</v>
+        <v>-0.6920009497189312</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1851961600057826</v>
+        <v>0.1912718023859563</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1870040749651783</v>
+        <v>0.1820370423124587</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3161,16 +3161,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4048135104644294</v>
+        <v>0.3469319991236262</v>
       </c>
       <c r="O4" s="5">
         <v>26</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2447629811958505</v>
+        <v>0.2357097584849076</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2371705533166854</v>
+        <v>0.2318733528080394</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
@@ -3220,16 +3220,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3831402272323127</v>
+        <v>-0.3381153975824418</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2408318814476925</v>
+        <v>0.2318591100268929</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1989016081063676</v>
+        <v>0.1946157326541046</v>
       </c>
       <c r="R5" s="5">
         <v>18</v>
@@ -3279,13 +3279,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.382991888710551</v>
+        <v>-1.382232571075292</v>
       </c>
       <c r="O6" s="5">
         <v>14</v>
       </c>
       <c r="P6" s="4">
-        <v>0.323424538819312</v>
+        <v>0.3234751599949959</v>
       </c>
       <c r="Q6" s="4">
         <v>0.3290022136160197</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.299847249525919</v>
+        <v>-1.251297412785789</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
@@ -3397,16 +3397,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.495780920030484</v>
+        <v>-1.490469771819335</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2286716283158512</v>
+        <v>0.228538752174245</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2286716283158512</v>
+        <v>0.228538752174245</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -3456,16 +3456,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.80410366475553</v>
+        <v>-1.883215549871238</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1881814804000896</v>
+        <v>0.1701322748504026</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1881814804000896</v>
+        <v>0.1701322748504026</v>
       </c>
       <c r="R9" s="5">
         <v>8</v>
@@ -3515,16 +3515,16 @@
         <v>2</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.883531121678061</v>
+        <v>-1.933217046629579</v>
       </c>
       <c r="O10" s="5">
         <v>8</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1191684838688616</v>
+        <v>0.1073811421183564</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1191684838688616</v>
+        <v>0.1073811421183564</v>
       </c>
       <c r="R10" s="5">
         <v>8</v>
@@ -3574,16 +3574,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.749240974255372</v>
+        <v>-1.711485369894945</v>
       </c>
       <c r="O11" s="5">
         <v>7</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1050492546901296</v>
+        <v>0.1041901873786628</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09008119972921642</v>
+        <v>0.08370575075033619</v>
       </c>
       <c r="R11" s="5">
         <v>7</v>
@@ -3633,7 +3633,7 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>-1.760440578121234</v>
+        <v>-1.786651554735727</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
@@ -3692,16 +3692,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.4069309936063031</v>
+        <v>-0.4234111965852208</v>
       </c>
       <c r="O13" s="5">
         <v>7</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1568663764563618</v>
+        <v>0.1527463257116324</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1614264154979574</v>
+        <v>0.1590721007866835</v>
       </c>
       <c r="R13" s="5">
         <v>7</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2254197946667773</v>
+        <v>0.1853411322481406</v>
       </c>
       <c r="O14" s="5">
         <v>8</v>
@@ -4157,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1977969175998253</v>
+        <v>-0.2938261739836889</v>
       </c>
       <c r="O3" s="5">
         <v>27</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2220999552965355</v>
+        <v>0.2115451355131236</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2346134498864593</v>
+        <v>0.2258420545044323</v>
       </c>
       <c r="R3" s="5">
         <v>27</v>
@@ -4216,16 +4216,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1104785695201826</v>
+        <v>-0.0503480764455162</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5783522458249796</v>
+        <v>0.5093236327184059</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3277019581814784</v>
+        <v>0.2375531445575926</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -4275,16 +4275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.29971220998737</v>
+        <v>-0.2758926957576477</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1037859932514057</v>
+        <v>0.09676427268509129</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09833992952621043</v>
+        <v>0.09240443930401751</v>
       </c>
       <c r="R5" s="5">
         <v>18</v>
@@ -4334,16 +4334,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7540701335742294</v>
+        <v>-0.7026271362774423</v>
       </c>
       <c r="O6" s="5">
         <v>15</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2471065215479919</v>
+        <v>0.2436769883948728</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2471065215479919</v>
+        <v>0.2436769883948728</v>
       </c>
       <c r="R6" s="5">
         <v>15</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7841958752156643</v>
+        <v>-0.6824862029206997</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2586681204006891</v>
+        <v>0.2432146670158545</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2586681204006891</v>
+        <v>0.2432146670158545</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7436087051200957</v>
+        <v>-0.7145270342953154</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.9338870976862381</v>
+        <v>-0.9449232420338376</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
@@ -4570,16 +4570,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.022221377260394</v>
+        <v>-1.035754604123213</v>
       </c>
       <c r="O10" s="5">
         <v>8</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1073706788722575</v>
+        <v>0.1041525087739501</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1073706788722575</v>
+        <v>0.1041525087739501</v>
       </c>
       <c r="R10" s="5">
         <v>8</v>
@@ -4629,16 +4629,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.9875981751001746</v>
+        <v>-0.9580972198018571</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09012563728742862</v>
+        <v>0.08588720230272884</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09012563728742862</v>
+        <v>0.08588720230272884</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.9082165159243232</v>
+        <v>-0.9679299899180478</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
@@ -4747,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.3820403287245426</v>
+        <v>-0.5155474487837637</v>
       </c>
       <c r="O13" s="5">
         <v>8</v>
       </c>
       <c r="P13" s="4">
-        <v>0.259453486856728</v>
+        <v>0.2035046084711212</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.259453486856728</v>
+        <v>0.2035046084711212</v>
       </c>
       <c r="R13" s="5">
         <v>8</v>
@@ -4806,16 +4806,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2763123825092667</v>
+        <v>-0.2562892937712604</v>
       </c>
       <c r="O14" s="5">
         <v>7</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3639937988262837</v>
+        <v>0.3589880266417822</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.09076265287817199</v>
+        <v>0.08790221162988539</v>
       </c>
       <c r="R14" s="5">
         <v>7</v>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04301374724491325</v>
+        <v>-0.06360896105252323</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3059258108656649</v>
+        <v>0.303866289484904</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3133880323930498</v>
@@ -5275,16 +5275,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4823371187328576</v>
+        <v>0.07031460618236451</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.635022682237478</v>
+        <v>0.4835513368042383</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4046368368272591</v>
+        <v>0.1401479276238596</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -5334,16 +5334,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4076491273414528</v>
+        <v>-0.4345977436569228</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.140119649526501</v>
+        <v>0.1410070145970427</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1194691489786742</v>
+        <v>0.1160129721750612</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9813708420639159</v>
+        <v>-1.014206218016625</v>
       </c>
       <c r="O6" s="5">
         <v>10</v>
@@ -5452,16 +5452,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7584843255841406</v>
+        <v>-0.6084358010848518</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3040231365058571</v>
+        <v>0.2740134316059993</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3040231365058571</v>
+        <v>0.2740134316059993</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -5625,16 +5625,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.28700397539651</v>
+        <v>-1.225690739083802</v>
       </c>
       <c r="O10" s="5">
         <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2374246492848033</v>
+        <v>0.2251620020222617</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2374246492848033</v>
+        <v>0.2251620020222617</v>
       </c>
       <c r="R10" s="5">
         <v>5</v>
@@ -5684,16 +5684,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.114099654718302</v>
+        <v>-1.131895671089296</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1267061194084818</v>
+        <v>0.1231469161342829</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1267061194084818</v>
+        <v>0.1231469161342829</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -5743,16 +5743,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-1.067829898577475</v>
+        <v>-0.9953919151739683</v>
       </c>
       <c r="O12" s="5">
         <v>5</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3296979836182436</v>
+        <v>0.3152103869375423</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.3296979836182436</v>
+        <v>0.3152103869375423</v>
       </c>
       <c r="R12" s="5">
         <v>5</v>
@@ -6039,16 +6039,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1282490795581662</v>
+        <v>-0.1894022572920155</v>
       </c>
       <c r="O3" s="5">
         <v>28</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2297002067288433</v>
+        <v>0.2276335661698104</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2168239353113269</v>
+        <v>0.2123518269161887</v>
       </c>
       <c r="R3" s="5">
         <v>28</v>
@@ -6098,16 +6098,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0182629717302122</v>
+        <v>0.04953025369877651</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1734300204422115</v>
+        <v>0.1682180427853915</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1421124570702214</v>
+        <v>0.1371268878344651</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -6157,16 +6157,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1841980677440412</v>
+        <v>-0.1859416719823912</v>
       </c>
       <c r="O5" s="5">
         <v>19</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09953570787222582</v>
+        <v>0.09953034498227921</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09009820710661151</v>
+        <v>0.09000022880044439</v>
       </c>
       <c r="R5" s="5">
         <v>19</v>
@@ -6216,16 +6216,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4103203168230823</v>
+        <v>-0.5552340391807888</v>
       </c>
       <c r="O6" s="5">
         <v>15</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3003492603363602</v>
+        <v>0.2663502087634705</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3003492603363602</v>
+        <v>0.2663502087634705</v>
       </c>
       <c r="R6" s="5">
         <v>15</v>
@@ -6275,16 +6275,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.403405546631349</v>
+        <v>-0.4812903321033977</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1971213667192278</v>
+        <v>0.1797576792139992</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1971213667192278</v>
+        <v>0.1797576792139992</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -6334,16 +6334,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4147295765462073</v>
+        <v>-0.6425351378235717</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4097409922221952</v>
+        <v>0.3272001605148096</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4097409922221952</v>
+        <v>0.3272001605148096</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -6393,16 +6393,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5362153797759053</v>
+        <v>-0.6812177414086626</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2958781729297502</v>
+        <v>0.263094334064478</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2958781729297502</v>
+        <v>0.263094334064478</v>
       </c>
       <c r="R9" s="5">
         <v>8</v>
@@ -6452,16 +6452,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.6393366816994424</v>
+        <v>-0.7074254274723533</v>
       </c>
       <c r="O10" s="5">
         <v>8</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1653649305885756</v>
+        <v>0.1472239847322308</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1653649305885756</v>
+        <v>0.1472239847322308</v>
       </c>
       <c r="R10" s="5">
         <v>8</v>
@@ -6511,16 +6511,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6954530147458589</v>
+        <v>-0.7094270912338096</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.05381761811563945</v>
+        <v>0.05105662782066078</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.05381761811563945</v>
+        <v>0.05105662782066078</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -6570,16 +6570,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.4810800382709477</v>
+        <v>-0.5628179087586176</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2035895044078919</v>
+        <v>0.1895637792720724</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2035895044078919</v>
+        <v>0.1895637792720724</v>
       </c>
       <c r="R12" s="5">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2816853819823777</v>
+        <v>-0.2986624649447123</v>
       </c>
       <c r="O13" s="5">
         <v>8</v>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2610702867798302</v>
+        <v>-0.2551747903709511</v>
       </c>
       <c r="O14" s="5">
         <v>8</v>
